--- a/docs/ValueSet-ahip-religion-spirituality.xlsx
+++ b/docs/ValueSet-ahip-religion-spirituality.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on HL7 Religion Value Set</t>
+    <t>Used as the answer options for the religion, spirituality, or belief system question in the Spirituality and Other Considerations Section.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -252,7 +252,7 @@
     <t>Spiritual but not religious</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
   </si>
   <si>
     <t>PSIN</t>
@@ -267,7 +267,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
   <si>
     <t>ASKU</t>

--- a/docs/ValueSet-ahip-religion-spirituality.xlsx
+++ b/docs/ValueSet-ahip-religion-spirituality.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -255,10 +255,13 @@
     <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
   </si>
   <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>Asked but unknown</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -268,15 +271,6 @@
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
-  </si>
-  <si>
-    <t>ASKU</t>
-  </si>
-  <si>
-    <t>Asked but unknown</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -802,7 +796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -827,26 +821,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -873,10 +859,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -892,7 +878,7 @@
         <v>70</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-religion-spirituality.xlsx
+++ b/docs/ValueSet-ahip-religion-spirituality.xlsx
@@ -96,7 +96,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -117,13 +118,13 @@
     <t>1004</t>
   </si>
   <si>
-    <t>Agnostic (not sure if there is a God)​</t>
+    <t>Agnostic (not sure if there is a God)</t>
   </si>
   <si>
     <t>1007</t>
   </si>
   <si>
-    <t>Atheist (do not believe in God)​</t>
+    <t>Atheist (do not believe in God)</t>
   </si>
   <si>
     <t>1008</t>
@@ -132,108 +133,108 @@
     <t>Baha'I</t>
   </si>
   <si>
-    <t>1059</t>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>Church of Scientology</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>Confucianism</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>Hinduism</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Humanism</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>Islam, Nation of Islam (Muslim)</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>Jehovah's Witnesses</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Judaism (Jewish)</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Mormonism (Church of Jesus Christ of Latter-day Saints/LDS)</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Paganism</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Shamanism</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>Sikhism</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>Taoism</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>VooDoo</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>Zoroastrianism</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
+  </si>
+  <si>
+    <t>BUDD</t>
   </si>
   <si>
     <t>Buddhism</t>
   </si>
   <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>Church of Scientology</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>Confucianism</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>Hinduism</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>Humanism</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>Islam,Nation of Islam (Muslim)</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>Jehovah's Witnesses</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>Judaism (Jewish)</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>Mormonism (Church of Jesus Christ of Latterday Saints/LDS)</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>Paganism</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>Shamanism</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>Sikhism</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>Taoism</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>Unitarian Universalist</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>VooDoo</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>Zoroastrianism</t>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
-  </si>
-  <si>
     <t>CHRI</t>
   </si>
   <si>
@@ -252,13 +253,13 @@
     <t>Spiritual but not religious</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
   </si>
   <si>
     <t>ASKU</t>
   </si>
   <si>
-    <t>Asked but unknown</t>
+    <t>I don't know</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
@@ -270,7 +271,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -536,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -705,26 +706,18 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -751,41 +744,49 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>78</v>
       </c>
     </row>
@@ -829,7 +830,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>81</v>
@@ -875,7 +876,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>84</v>
